--- a/reports/Debug-purgatory-20260105/Week Total (Prior Year)_Visits.xlsx
+++ b/reports/Debug-purgatory-20260105/Week Total (Prior Year)_Visits.xlsx
@@ -34,7 +34,7 @@
     <t>Purgatory Passes</t>
   </si>
   <si>
-    <t>Purgatory Tickets</t>
+    <t>Purgatory Coaster</t>
   </si>
   <si>
     <t>Purgatory Comp Tickets</t>
@@ -43,7 +43,7 @@
     <t>Purgatory Uplift Tickets</t>
   </si>
   <si>
-    <t>Purgatory Coaster</t>
+    <t>Purgatory Tickets</t>
   </si>
 </sst>
 </file>
@@ -434,10 +434,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>45664</v>
+        <v>45663</v>
       </c>
       <c r="C2" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -448,10 +448,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>45664</v>
+        <v>45663</v>
       </c>
       <c r="C3" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>5</v>
@@ -462,10 +462,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="2">
-        <v>45665</v>
+        <v>45663</v>
       </c>
       <c r="C4" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>5</v>
@@ -476,13 +476,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2">
-        <v>45665</v>
+        <v>45664</v>
       </c>
       <c r="C5" s="2">
-        <v>995</v>
+        <v>5</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -490,13 +490,13 @@
         <v>1</v>
       </c>
       <c r="B6" s="2">
-        <v>45666</v>
+        <v>45664</v>
       </c>
       <c r="C6" s="2">
-        <v>832</v>
+        <v>2</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -504,10 +504,10 @@
         <v>1</v>
       </c>
       <c r="B7" s="2">
-        <v>45667</v>
+        <v>45665</v>
       </c>
       <c r="C7" s="2">
-        <v>10</v>
+        <v>167</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>5</v>
@@ -518,10 +518,10 @@
         <v>1</v>
       </c>
       <c r="B8" s="2">
-        <v>45667</v>
+        <v>45666</v>
       </c>
       <c r="C8" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>5</v>
@@ -532,10 +532,10 @@
         <v>1</v>
       </c>
       <c r="B9" s="2">
-        <v>45668</v>
+        <v>45666</v>
       </c>
       <c r="C9" s="2">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>5</v>
@@ -546,13 +546,13 @@
         <v>1</v>
       </c>
       <c r="B10" s="2">
-        <v>45668</v>
+        <v>45666</v>
       </c>
       <c r="C10" s="2">
-        <v>988</v>
+        <v>7</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -560,10 +560,10 @@
         <v>1</v>
       </c>
       <c r="B11" s="2">
-        <v>45668</v>
+        <v>45667</v>
       </c>
       <c r="C11" s="2">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>5</v>
@@ -574,13 +574,13 @@
         <v>1</v>
       </c>
       <c r="B12" s="2">
-        <v>45669</v>
+        <v>45667</v>
       </c>
       <c r="C12" s="2">
-        <v>1847</v>
+        <v>201</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -588,13 +588,13 @@
         <v>1</v>
       </c>
       <c r="B13" s="2">
-        <v>45663</v>
+        <v>45668</v>
       </c>
       <c r="C13" s="2">
-        <v>238</v>
+        <v>148</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -602,10 +602,10 @@
         <v>1</v>
       </c>
       <c r="B14" s="2">
-        <v>45663</v>
+        <v>45669</v>
       </c>
       <c r="C14" s="2">
-        <v>899</v>
+        <v>1</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>5</v>
@@ -616,10 +616,10 @@
         <v>1</v>
       </c>
       <c r="B15" s="2">
-        <v>45664</v>
+        <v>45669</v>
       </c>
       <c r="C15" s="2">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>5</v>
@@ -630,10 +630,10 @@
         <v>1</v>
       </c>
       <c r="B16" s="2">
-        <v>45665</v>
+        <v>45669</v>
       </c>
       <c r="C16" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>5</v>
@@ -644,10 +644,10 @@
         <v>1</v>
       </c>
       <c r="B17" s="2">
-        <v>45665</v>
+        <v>45663</v>
       </c>
       <c r="C17" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>5</v>
@@ -658,13 +658,13 @@
         <v>1</v>
       </c>
       <c r="B18" s="2">
-        <v>45666</v>
+        <v>45664</v>
       </c>
       <c r="C18" s="2">
-        <v>236</v>
+        <v>5</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -672,13 +672,13 @@
         <v>1</v>
       </c>
       <c r="B19" s="2">
-        <v>45666</v>
+        <v>45664</v>
       </c>
       <c r="C19" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -686,10 +686,10 @@
         <v>1</v>
       </c>
       <c r="B20" s="2">
-        <v>45667</v>
+        <v>45664</v>
       </c>
       <c r="C20" s="2">
-        <v>125</v>
+        <v>2</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>5</v>
@@ -700,10 +700,10 @@
         <v>1</v>
       </c>
       <c r="B21" s="2">
-        <v>45669</v>
+        <v>45666</v>
       </c>
       <c r="C21" s="2">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>5</v>
@@ -714,13 +714,13 @@
         <v>1</v>
       </c>
       <c r="B22" s="2">
-        <v>45669</v>
+        <v>45667</v>
       </c>
       <c r="C22" s="2">
-        <v>173</v>
+        <v>5</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -728,10 +728,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2">
-        <v>45663</v>
+        <v>45667</v>
       </c>
       <c r="C23" s="2">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>5</v>
@@ -742,13 +742,13 @@
         <v>1</v>
       </c>
       <c r="B24" s="2">
-        <v>45664</v>
+        <v>45667</v>
       </c>
       <c r="C24" s="2">
-        <v>1069</v>
+        <v>15</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -756,10 +756,10 @@
         <v>1</v>
       </c>
       <c r="B25" s="2">
-        <v>45665</v>
+        <v>45668</v>
       </c>
       <c r="C25" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>5</v>
@@ -770,7 +770,7 @@
         <v>1</v>
       </c>
       <c r="B26" s="2">
-        <v>45665</v>
+        <v>45669</v>
       </c>
       <c r="C26" s="2">
         <v>3</v>
@@ -784,10 +784,10 @@
         <v>1</v>
       </c>
       <c r="B27" s="2">
-        <v>45666</v>
+        <v>45669</v>
       </c>
       <c r="C27" s="2">
-        <v>3</v>
+        <v>126</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>5</v>
@@ -798,10 +798,10 @@
         <v>1</v>
       </c>
       <c r="B28" s="2">
-        <v>45666</v>
+        <v>45663</v>
       </c>
       <c r="C28" s="2">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>5</v>
@@ -812,10 +812,10 @@
         <v>1</v>
       </c>
       <c r="B29" s="2">
-        <v>45667</v>
+        <v>45665</v>
       </c>
       <c r="C29" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>5</v>
@@ -826,13 +826,13 @@
         <v>1</v>
       </c>
       <c r="B30" s="2">
-        <v>45668</v>
+        <v>45665</v>
       </c>
       <c r="C30" s="2">
-        <v>23</v>
+        <v>226</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -840,13 +840,13 @@
         <v>1</v>
       </c>
       <c r="B31" s="2">
-        <v>45668</v>
+        <v>45665</v>
       </c>
       <c r="C31" s="2">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -854,10 +854,10 @@
         <v>1</v>
       </c>
       <c r="B32" s="2">
-        <v>45668</v>
+        <v>45665</v>
       </c>
       <c r="C32" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>5</v>
@@ -868,10 +868,10 @@
         <v>1</v>
       </c>
       <c r="B33" s="2">
-        <v>45669</v>
+        <v>45666</v>
       </c>
       <c r="C33" s="2">
-        <v>3</v>
+        <v>94</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>5</v>
@@ -882,10 +882,10 @@
         <v>1</v>
       </c>
       <c r="B34" s="2">
-        <v>45663</v>
+        <v>45668</v>
       </c>
       <c r="C34" s="2">
-        <v>98</v>
+        <v>43</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>5</v>
@@ -896,13 +896,13 @@
         <v>1</v>
       </c>
       <c r="B35" s="2">
-        <v>45665</v>
+        <v>45668</v>
       </c>
       <c r="C35" s="2">
-        <v>3</v>
+        <v>268</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -910,13 +910,13 @@
         <v>1</v>
       </c>
       <c r="B36" s="2">
-        <v>45665</v>
+        <v>45668</v>
       </c>
       <c r="C36" s="2">
-        <v>226</v>
+        <v>3</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -924,13 +924,13 @@
         <v>1</v>
       </c>
       <c r="B37" s="2">
-        <v>45665</v>
+        <v>45669</v>
       </c>
       <c r="C37" s="2">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -938,10 +938,10 @@
         <v>1</v>
       </c>
       <c r="B38" s="2">
-        <v>45665</v>
+        <v>45664</v>
       </c>
       <c r="C38" s="2">
-        <v>115</v>
+        <v>751</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>5</v>
@@ -952,10 +952,10 @@
         <v>1</v>
       </c>
       <c r="B39" s="2">
-        <v>45666</v>
+        <v>45664</v>
       </c>
       <c r="C39" s="2">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>5</v>
@@ -966,10 +966,10 @@
         <v>1</v>
       </c>
       <c r="B40" s="2">
-        <v>45668</v>
+        <v>45666</v>
       </c>
       <c r="C40" s="2">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>5</v>
@@ -980,13 +980,13 @@
         <v>1</v>
       </c>
       <c r="B41" s="2">
-        <v>45668</v>
+        <v>45667</v>
       </c>
       <c r="C41" s="2">
-        <v>268</v>
+        <v>1406</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -994,13 +994,13 @@
         <v>1</v>
       </c>
       <c r="B42" s="2">
-        <v>45668</v>
+        <v>45667</v>
       </c>
       <c r="C42" s="2">
-        <v>3</v>
+        <v>869</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1008,13 +1008,13 @@
         <v>1</v>
       </c>
       <c r="B43" s="2">
-        <v>45669</v>
+        <v>45667</v>
       </c>
       <c r="C43" s="2">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1022,13 +1022,13 @@
         <v>1</v>
       </c>
       <c r="B44" s="2">
-        <v>45663</v>
+        <v>45667</v>
       </c>
       <c r="C44" s="2">
-        <v>1071</v>
+        <v>135</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1036,10 +1036,10 @@
         <v>1</v>
       </c>
       <c r="B45" s="2">
-        <v>45663</v>
+        <v>45669</v>
       </c>
       <c r="C45" s="2">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>5</v>
@@ -1050,10 +1050,10 @@
         <v>1</v>
       </c>
       <c r="B46" s="2">
-        <v>45663</v>
+        <v>45664</v>
       </c>
       <c r="C46" s="2">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>5</v>
@@ -1067,10 +1067,10 @@
         <v>45664</v>
       </c>
       <c r="C47" s="2">
-        <v>219</v>
+        <v>5</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1078,13 +1078,13 @@
         <v>1</v>
       </c>
       <c r="B48" s="2">
-        <v>45664</v>
+        <v>45665</v>
       </c>
       <c r="C48" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1095,10 +1095,10 @@
         <v>45665</v>
       </c>
       <c r="C49" s="2">
-        <v>1322</v>
+        <v>995</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1106,10 +1106,10 @@
         <v>1</v>
       </c>
       <c r="B50" s="2">
-        <v>45665</v>
+        <v>45666</v>
       </c>
       <c r="C50" s="2">
-        <v>1</v>
+        <v>832</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>5</v>
@@ -1120,13 +1120,13 @@
         <v>1</v>
       </c>
       <c r="B51" s="2">
-        <v>45666</v>
+        <v>45667</v>
       </c>
       <c r="C51" s="2">
-        <v>828</v>
+        <v>10</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1134,7 +1134,7 @@
         <v>1</v>
       </c>
       <c r="B52" s="2">
-        <v>45666</v>
+        <v>45667</v>
       </c>
       <c r="C52" s="2">
         <v>4</v>
@@ -1148,10 +1148,10 @@
         <v>1</v>
       </c>
       <c r="B53" s="2">
-        <v>45666</v>
+        <v>45668</v>
       </c>
       <c r="C53" s="2">
-        <v>133</v>
+        <v>1</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>5</v>
@@ -1162,13 +1162,13 @@
         <v>1</v>
       </c>
       <c r="B54" s="2">
-        <v>45667</v>
+        <v>45668</v>
       </c>
       <c r="C54" s="2">
-        <v>8</v>
+        <v>988</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1179,7 +1179,7 @@
         <v>45668</v>
       </c>
       <c r="C55" s="2">
-        <v>2250</v>
+        <v>36</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>5</v>
@@ -1193,10 +1193,10 @@
         <v>45669</v>
       </c>
       <c r="C56" s="2">
-        <v>563</v>
+        <v>1847</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1204,13 +1204,13 @@
         <v>1</v>
       </c>
       <c r="B57" s="2">
-        <v>45669</v>
+        <v>45663</v>
       </c>
       <c r="C57" s="2">
-        <v>3</v>
+        <v>1071</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1218,10 +1218,10 @@
         <v>1</v>
       </c>
       <c r="B58" s="2">
-        <v>45669</v>
+        <v>45663</v>
       </c>
       <c r="C58" s="2">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>5</v>
@@ -1235,7 +1235,7 @@
         <v>45663</v>
       </c>
       <c r="C59" s="2">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>5</v>
@@ -1249,10 +1249,10 @@
         <v>45664</v>
       </c>
       <c r="C60" s="2">
-        <v>5</v>
+        <v>219</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1263,10 +1263,10 @@
         <v>45664</v>
       </c>
       <c r="C61" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1274,10 +1274,10 @@
         <v>1</v>
       </c>
       <c r="B62" s="2">
-        <v>45664</v>
+        <v>45665</v>
       </c>
       <c r="C62" s="2">
-        <v>2</v>
+        <v>1322</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>5</v>
@@ -1288,7 +1288,7 @@
         <v>1</v>
       </c>
       <c r="B63" s="2">
-        <v>45666</v>
+        <v>45665</v>
       </c>
       <c r="C63" s="2">
         <v>1</v>
@@ -1302,13 +1302,13 @@
         <v>1</v>
       </c>
       <c r="B64" s="2">
-        <v>45667</v>
+        <v>45666</v>
       </c>
       <c r="C64" s="2">
-        <v>5</v>
+        <v>828</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1316,10 +1316,10 @@
         <v>1</v>
       </c>
       <c r="B65" s="2">
-        <v>45667</v>
+        <v>45666</v>
       </c>
       <c r="C65" s="2">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>5</v>
@@ -1330,10 +1330,10 @@
         <v>1</v>
       </c>
       <c r="B66" s="2">
-        <v>45667</v>
+        <v>45666</v>
       </c>
       <c r="C66" s="2">
-        <v>15</v>
+        <v>133</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>5</v>
@@ -1344,13 +1344,13 @@
         <v>1</v>
       </c>
       <c r="B67" s="2">
-        <v>45668</v>
+        <v>45667</v>
       </c>
       <c r="C67" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1358,10 +1358,10 @@
         <v>1</v>
       </c>
       <c r="B68" s="2">
-        <v>45669</v>
+        <v>45668</v>
       </c>
       <c r="C68" s="2">
-        <v>3</v>
+        <v>2250</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>5</v>
@@ -1375,10 +1375,10 @@
         <v>45669</v>
       </c>
       <c r="C69" s="2">
-        <v>126</v>
+        <v>563</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1386,10 +1386,10 @@
         <v>1</v>
       </c>
       <c r="B70" s="2">
-        <v>45664</v>
+        <v>45669</v>
       </c>
       <c r="C70" s="2">
-        <v>751</v>
+        <v>3</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>5</v>
@@ -1400,10 +1400,10 @@
         <v>1</v>
       </c>
       <c r="B71" s="2">
-        <v>45664</v>
+        <v>45669</v>
       </c>
       <c r="C71" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>5</v>
@@ -1414,10 +1414,10 @@
         <v>1</v>
       </c>
       <c r="B72" s="2">
-        <v>45666</v>
+        <v>45663</v>
       </c>
       <c r="C72" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>5</v>
@@ -1428,13 +1428,13 @@
         <v>1</v>
       </c>
       <c r="B73" s="2">
-        <v>45667</v>
+        <v>45664</v>
       </c>
       <c r="C73" s="2">
-        <v>1406</v>
+        <v>1069</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -1442,13 +1442,13 @@
         <v>1</v>
       </c>
       <c r="B74" s="2">
-        <v>45667</v>
+        <v>45665</v>
       </c>
       <c r="C74" s="2">
-        <v>869</v>
+        <v>4</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -1456,10 +1456,10 @@
         <v>1</v>
       </c>
       <c r="B75" s="2">
-        <v>45667</v>
+        <v>45665</v>
       </c>
       <c r="C75" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>5</v>
@@ -1470,10 +1470,10 @@
         <v>1</v>
       </c>
       <c r="B76" s="2">
-        <v>45667</v>
+        <v>45666</v>
       </c>
       <c r="C76" s="2">
-        <v>135</v>
+        <v>3</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>5</v>
@@ -1484,10 +1484,10 @@
         <v>1</v>
       </c>
       <c r="B77" s="2">
-        <v>45669</v>
+        <v>45666</v>
       </c>
       <c r="C77" s="2">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>5</v>
@@ -1498,10 +1498,10 @@
         <v>1</v>
       </c>
       <c r="B78" s="2">
-        <v>45663</v>
+        <v>45667</v>
       </c>
       <c r="C78" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>5</v>
@@ -1512,10 +1512,10 @@
         <v>1</v>
       </c>
       <c r="B79" s="2">
-        <v>45663</v>
+        <v>45668</v>
       </c>
       <c r="C79" s="2">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>5</v>
@@ -1526,10 +1526,10 @@
         <v>1</v>
       </c>
       <c r="B80" s="2">
-        <v>45663</v>
+        <v>45668</v>
       </c>
       <c r="C80" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>5</v>
@@ -1540,10 +1540,10 @@
         <v>1</v>
       </c>
       <c r="B81" s="2">
-        <v>45664</v>
+        <v>45668</v>
       </c>
       <c r="C81" s="2">
-        <v>5</v>
+        <v>117</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>5</v>
@@ -1554,13 +1554,13 @@
         <v>1</v>
       </c>
       <c r="B82" s="2">
-        <v>45664</v>
+        <v>45669</v>
       </c>
       <c r="C82" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -1568,13 +1568,13 @@
         <v>1</v>
       </c>
       <c r="B83" s="2">
-        <v>45665</v>
+        <v>45663</v>
       </c>
       <c r="C83" s="2">
-        <v>167</v>
+        <v>238</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -1582,10 +1582,10 @@
         <v>1</v>
       </c>
       <c r="B84" s="2">
-        <v>45666</v>
+        <v>45663</v>
       </c>
       <c r="C84" s="2">
-        <v>3</v>
+        <v>899</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>5</v>
@@ -1596,10 +1596,10 @@
         <v>1</v>
       </c>
       <c r="B85" s="2">
-        <v>45666</v>
+        <v>45664</v>
       </c>
       <c r="C85" s="2">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>5</v>
@@ -1610,10 +1610,10 @@
         <v>1</v>
       </c>
       <c r="B86" s="2">
-        <v>45666</v>
+        <v>45665</v>
       </c>
       <c r="C86" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>5</v>
@@ -1624,10 +1624,10 @@
         <v>1</v>
       </c>
       <c r="B87" s="2">
-        <v>45667</v>
+        <v>45665</v>
       </c>
       <c r="C87" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>5</v>
@@ -1638,10 +1638,10 @@
         <v>1</v>
       </c>
       <c r="B88" s="2">
-        <v>45667</v>
+        <v>45666</v>
       </c>
       <c r="C88" s="2">
-        <v>201</v>
+        <v>236</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>7</v>
@@ -1652,13 +1652,13 @@
         <v>1</v>
       </c>
       <c r="B89" s="2">
-        <v>45668</v>
+        <v>45666</v>
       </c>
       <c r="C89" s="2">
-        <v>148</v>
+        <v>4</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -1666,10 +1666,10 @@
         <v>1</v>
       </c>
       <c r="B90" s="2">
-        <v>45669</v>
+        <v>45667</v>
       </c>
       <c r="C90" s="2">
-        <v>1</v>
+        <v>125</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>5</v>
@@ -1683,7 +1683,7 @@
         <v>45669</v>
       </c>
       <c r="C91" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>5</v>
@@ -1697,10 +1697,10 @@
         <v>45669</v>
       </c>
       <c r="C92" s="2">
-        <v>1</v>
+        <v>173</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
